--- a/nr-update-idnatstruct-descr/ig/StructureDefinition-fr-core-observation-body-height.xlsx
+++ b/nr-update-idnatstruct-descr/ig/StructureDefinition-fr-core-observation-body-height.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T15:39:50+00:00</t>
+    <t>2025-02-04T15:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
